--- a/excel/M3_Complaint_Labeling.xlsx
+++ b/excel/M3_Complaint_Labeling.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac1/Desktop/app_projects/supplier-data-health-check/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C691F1-23AB-0A43-A298-82649F2F5D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3B36B8-8CF9-D04A-B3D1-CC03A6249113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
